--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260819.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260819.xlsx
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>26,540,060</t>
+          <t>70,218,324</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>70,218,324</t>
+          <t>26,540,060</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
